--- a/data/trans_orig/IMC-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IMC-Estudios-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>IMC Adultos</t>
+          <t>IMC Adultos (tasa de respuesta: 96,87%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>26,64; 27,13</t>
+          <t>26,62; 27,14</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>27,28; 27,85</t>
+          <t>27,3; 27,86</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>27,28; 27,92</t>
+          <t>27,26; 27,92</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>27,55; 28,28</t>
+          <t>27,54; 28,33</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>27,16; 27,66</t>
+          <t>27,16; 27,69</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>28,24; 28,83</t>
+          <t>28,23; 28,83</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>28,13; 28,87</t>
+          <t>28,13; 28,93</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>27,64; 28,21</t>
+          <t>27,66; 28,22</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>26,99; 27,37</t>
+          <t>27,0; 27,36</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>27,92; 28,31</t>
+          <t>27,92; 28,32</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>27,84; 28,37</t>
+          <t>27,85; 28,35</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>27,7; 28,16</t>
+          <t>27,68; 28,14</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>25,46; 25,78</t>
+          <t>25,46; 25,77</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>26,19; 26,54</t>
+          <t>26,18; 26,55</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>26,05; 26,43</t>
+          <t>26,07; 26,44</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>26,47; 28,01</t>
+          <t>26,48; 27,91</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>24,04; 24,46</t>
+          <t>24,02; 24,45</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>25,07; 25,55</t>
+          <t>25,05; 25,51</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>25,09; 25,54</t>
+          <t>25,08; 25,53</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>25,49; 28,9</t>
+          <t>25,5; 28,9</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>24,83; 25,09</t>
+          <t>24,84; 25,11</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>25,72; 26,02</t>
+          <t>25,71; 26,0</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>25,63; 25,93</t>
+          <t>25,65; 25,95</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>26,08; 27,87</t>
+          <t>26,12; 27,96</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>25,35; 25,97</t>
+          <t>25,38; 25,95</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>25,71; 26,38</t>
+          <t>25,7; 26,35</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>25,54; 26,25</t>
+          <t>25,52; 26,22</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>25,83; 26,49</t>
+          <t>25,83; 26,47</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>23,2; 24,0</t>
+          <t>23,21; 24,01</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>23,37; 24,07</t>
+          <t>23,37; 24,09</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>23,93; 24,69</t>
+          <t>23,93; 24,67</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>24,29; 24,92</t>
+          <t>24,31; 24,91</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>24,45; 24,95</t>
+          <t>24,46; 24,97</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>24,65; 25,16</t>
+          <t>24,65; 25,15</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>24,84; 25,35</t>
+          <t>24,83; 25,36</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>25,14; 25,6</t>
+          <t>25,14; 25,58</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>25,89; 26,14</t>
+          <t>25,89; 26,15</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>26,52; 26,81</t>
+          <t>26,52; 26,8</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>26,34; 26,64</t>
+          <t>26,32; 26,63</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>26,61; 27,71</t>
+          <t>26,62; 27,62</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>25,22; 25,54</t>
+          <t>25,21; 25,55</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>26,08; 26,44</t>
+          <t>26,07; 26,45</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>25,82; 26,16</t>
+          <t>25,83; 26,19</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>25,83; 28,06</t>
+          <t>25,83; 28,03</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>25,59; 25,79</t>
+          <t>25,59; 25,8</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>26,34; 26,56</t>
+          <t>26,35; 26,56</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>26,12; 26,35</t>
+          <t>26,13; 26,35</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>26,28; 27,55</t>
+          <t>26,27; 27,32</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IMC-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IMC-Estudios-trans_orig.xlsx
@@ -663,47 +663,47 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
+          <t>27,83</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>27,42</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>28,53</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>28,49</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>27,99</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>27,18</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>28,12</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>28,09</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
           <t>27,92</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>27,42</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>28,53</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>28,49</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>27,93</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>27,18</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>28,12</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>28,09</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>27,93</t>
         </is>
       </c>
     </row>
@@ -716,12 +716,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>26,62; 27,14</t>
+          <t>26,63; 27,16</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>27,3; 27,86</t>
+          <t>27,31; 27,9</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -731,47 +731,47 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>27,54; 28,33</t>
+          <t>27,49; 28,21</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>27,16; 27,69</t>
+          <t>27,18; 27,71</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>28,23; 28,83</t>
+          <t>28,25; 28,83</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>28,13; 28,93</t>
+          <t>28,13; 28,88</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>27,66; 28,22</t>
+          <t>27,73; 28,28</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>27,0; 27,36</t>
+          <t>27,0; 27,37</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>27,92; 28,32</t>
+          <t>27,91; 28,31</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>27,85; 28,35</t>
+          <t>27,84; 28,36</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>27,68; 28,14</t>
+          <t>27,7; 28,15</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>26,94</t>
+          <t>26,53</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>26,38</t>
+          <t>25,57</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>26,67</t>
+          <t>26,06</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>25,46; 25,77</t>
+          <t>25,47; 25,79</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>26,18; 26,55</t>
+          <t>26,18; 26,54</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>26,07; 26,44</t>
+          <t>26,06; 26,45</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>26,48; 27,91</t>
+          <t>26,32; 26,76</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>24,02; 24,45</t>
+          <t>24,02; 24,44</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>25,05; 25,51</t>
+          <t>25,06; 25,54</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>25,08; 25,53</t>
+          <t>25,09; 25,53</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>25,5; 28,9</t>
+          <t>25,39; 25,76</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>24,84; 25,11</t>
+          <t>24,83; 25,09</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>25,71; 26,0</t>
+          <t>25,71; 26,02</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>25,65; 25,95</t>
+          <t>25,64; 25,93</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>26,12; 27,96</t>
+          <t>25,91; 26,2</t>
         </is>
       </c>
     </row>
@@ -943,7 +943,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>26,14</t>
+          <t>26,06</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>24,59</t>
+          <t>24,68</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>25,38; 25,95</t>
+          <t>25,36; 25,93</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>25,7; 26,35</t>
+          <t>25,67; 26,35</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>25,52; 26,22</t>
+          <t>25,53; 26,22</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>25,83; 26,47</t>
+          <t>25,77; 26,39</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>23,21; 24,01</t>
+          <t>23,22; 24,01</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>23,37; 24,09</t>
+          <t>23,33; 24,05</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>23,93; 24,67</t>
+          <t>23,95; 24,73</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>24,31; 24,91</t>
+          <t>24,4; 25,03</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>24,46; 24,97</t>
+          <t>24,42; 24,93</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>24,65; 25,15</t>
+          <t>24,64; 25,16</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>24,83; 25,36</t>
+          <t>24,84; 25,35</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>25,14; 25,58</t>
+          <t>25,14; 25,59</t>
         </is>
       </c>
     </row>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>26,93</t>
+          <t>26,64</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>26,36</t>
+          <t>25,9</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>26,64</t>
+          <t>26,26</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>25,89; 26,15</t>
+          <t>25,9; 26,15</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>26,52; 26,8</t>
+          <t>26,5; 26,79</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>26,32; 26,63</t>
+          <t>26,34; 26,63</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>26,62; 27,62</t>
+          <t>26,49; 26,81</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>25,21; 25,55</t>
+          <t>25,22; 25,56</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>26,07; 26,45</t>
+          <t>26,07; 26,43</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>25,83; 26,19</t>
+          <t>25,82; 26,18</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>25,83; 28,03</t>
+          <t>25,76; 26,05</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>25,59; 25,8</t>
+          <t>25,59; 25,79</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>26,35; 26,56</t>
+          <t>26,33; 26,57</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>26,13; 26,35</t>
+          <t>26,11; 26,35</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>26,27; 27,32</t>
+          <t>26,15; 26,37</t>
         </is>
       </c>
     </row>
